--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486379_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486379_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1926</v>
+        <v>5.2986</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7445</v>
+        <v>5.9738</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.6752</v>
       </c>
       <c r="G2" t="n">
         <v>3.8688</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1988</v>
+        <v>0.9073</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8099</v>
+        <v>0.4194</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6112</v>
+        <v>0.4879</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5649999999999999</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. NGOM</t>
+          <t>J. TATE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.291</v>
+        <v>2.6359</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9971</v>
+        <v>3.8783</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-1.2424</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1348</v>
+        <v>3.5863</v>
       </c>
       <c r="H3" t="n">
-        <v>2.421</v>
+        <v>3.9082</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2861</v>
+        <v>-0.3219</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6546</v>
+        <v>5.7021</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5398</v>
+        <v>4.3251</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>1.377</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5197</v>
+        <v>-2.1158</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1188</v>
+        <v>-0.4169</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4009</v>
+        <v>-1.6989</v>
       </c>
       <c r="P3" t="n">
-        <v>0.435</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.305</v>
+        <v>-3.2626</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1355</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7367</v>
+        <v>0.3088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3988</v>
+        <v>-0.2364</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5857</v>
+        <v>0.9347</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9109</v>
+        <v>1.13</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. TATE</t>
+          <t>A. NGOM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3083</v>
+        <v>2.6167</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7665</v>
+        <v>3.6618</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4582</v>
+        <v>-1.0451</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5863</v>
+        <v>1.1348</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9082</v>
+        <v>2.421</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3219</v>
+        <v>-1.2861</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7021</v>
+        <v>2.6546</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3251</v>
+        <v>2.5398</v>
       </c>
       <c r="L4" t="n">
-        <v>1.377</v>
+        <v>0.1147</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1158</v>
+        <v>-1.5197</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4169</v>
+        <v>-0.1188</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6989</v>
+        <v>-1.4009</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9576</v>
+        <v>0.435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2626</v>
+        <v>-1.305</v>
       </c>
       <c r="R4" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2551</v>
+        <v>0.4612</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971</v>
+        <v>0.4014</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4522</v>
+        <v>0.0598</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>0.5857</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.9109</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="5">
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5306</v>
+        <v>1.4189</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1249</v>
+        <v>1.0131</v>
       </c>
       <c r="F5" t="n">
         <v>0.4057</v>
@@ -844,10 +844,10 @@
         <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7571</v>
+        <v>0.6453</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3461</v>
+        <v>0.2343</v>
       </c>
       <c r="U5" t="n">
         <v>0.411</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8363</v>
+        <v>1.029</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2829</v>
+        <v>0.5064</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5534</v>
+        <v>0.5226</v>
       </c>
       <c r="G6" t="n">
         <v>-2.4444</v>
@@ -922,13 +922,13 @@
         <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3066</v>
+        <v>-0.1139</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.399</v>
+        <v>-0.1754</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0924</v>
+        <v>0.0616</v>
       </c>
       <c r="V6" t="n">
         <v>2.0647</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7451</v>
+        <v>0.298</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7451</v>
+        <v>0.298</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7451</v>
+        <v>0.298</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7451</v>
+        <v>0.298</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3914</v>
+        <v>-0.3215</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1427</v>
+        <v>-0.8758</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5341</v>
+        <v>0.5543</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8954</v>
+        <v>-1.0516</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.328</v>
+        <v>0.4226</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.5674</v>
+        <v>-1.4742</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5032</v>
+        <v>-0.0338</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6562</v>
+        <v>1.5694</v>
       </c>
       <c r="L8" t="n">
-        <v>0.153</v>
+        <v>-1.6032</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.3922</v>
+        <v>-1.0178</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3282</v>
+        <v>-1.1468</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7204</v>
+        <v>0.1291</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6525</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R8" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3512</v>
+        <v>0.6877</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6682</v>
+        <v>0.2031</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.4846</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.4997</v>
+        <v>1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.718</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.056</v>
+        <v>0.1427</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.662</v>
+        <v>-1.0273</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.0266</v>
+        <v>-0.8954</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0314</v>
+        <v>-0.328</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0048</v>
+        <v>-0.5674</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1913</v>
+        <v>-0.5032</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.918</v>
+        <v>-0.6562</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7267</v>
+        <v>0.153</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8353</v>
+        <v>-0.3922</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1134</v>
+        <v>0.3282</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2781</v>
+        <v>-0.7204</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9834</v>
+        <v>0.858</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7677</v>
+        <v>0.6682</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2157</v>
+        <v>0.1899</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3698</v>
+        <v>-1.4997</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7602</v>
+        <v>0.1952</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.13</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3311</v>
+        <v>-1.6814</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5463</v>
+        <v>-1.1735</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2153</v>
+        <v>-0.5079</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0516</v>
+        <v>-1.0266</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4226</v>
+        <v>-2.0314</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4742</v>
+        <v>1.0048</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0338</v>
+        <v>-0.1913</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5694</v>
+        <v>-0.918</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6032</v>
+        <v>0.7267</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0178</v>
+        <v>-0.8353</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1468</v>
+        <v>-1.1134</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1291</v>
+        <v>0.2781</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.0875</v>
+        <v>-1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="R10" t="n">
         <v>1.0875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3219</v>
+        <v>1.0199</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4675</v>
+        <v>0.6501</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1455</v>
+        <v>0.3698</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="W10" t="n">
-        <v>1.13</v>
+        <v>0.7602</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>G. MAIZA APECECHEA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3096</v>
+        <v>-2.5138</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5147</v>
+        <v>-2.048</v>
       </c>
       <c r="F11" t="n">
-        <v>0.205</v>
+        <v>-0.4658</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.31</v>
+        <v>-0.8282</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5418</v>
+        <v>0.0698</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2319</v>
+        <v>-0.8981</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3178</v>
+        <v>0.6891</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.356</v>
+        <v>0.4197</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0382</v>
+        <v>0.2694</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0078</v>
+        <v>-1.5173</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1858</v>
+        <v>-0.3499</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1936</v>
+        <v>-1.1674</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.6101</v>
+        <v>-3.6976</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1956</v>
+        <v>-0.423</v>
       </c>
       <c r="T11" t="n">
-        <v>1.4132</v>
+        <v>-0.1694</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2176</v>
+        <v>-0.2536</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3252</v>
+        <v>1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.3252</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. MAIZA APECECHEA</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9609</v>
+        <v>-2.7028</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.495</v>
+        <v>-3.1852</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4658</v>
+        <v>0.4824</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8282</v>
+        <v>-1.31</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0698</v>
+        <v>-1.5418</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.8981</v>
+        <v>0.2319</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6891</v>
+        <v>-1.3178</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4197</v>
+        <v>-1.356</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2694</v>
+        <v>0.0382</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5173</v>
+        <v>0.0078</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.3499</v>
+        <v>-0.1858</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1674</v>
+        <v>0.1936</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.3926</v>
+        <v>-0.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.6976</v>
+        <v>-2.6101</v>
       </c>
       <c r="R12" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.87</v>
+        <v>0.8024</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6165</v>
+        <v>0.7427</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2536</v>
+        <v>0.0598</v>
       </c>
       <c r="V12" t="n">
-        <v>1.13</v>
+        <v>-1.3252</v>
       </c>
       <c r="W12" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="13">
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.192899999999998</v>
+        <v>5.192999999999998</v>
       </c>
       <c r="E13" t="n">
-        <v>8.191699999999997</v>
+        <v>8.191600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9987</v>
+        <v>-2.998699999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4978</v>
+        <v>-0.4978000000000002</v>
       </c>
       <c r="H13" t="n">
         <v>2.1597</v>
@@ -1444,10 +1444,10 @@
         <v>11.2774</v>
       </c>
       <c r="K13" t="n">
-        <v>8.3207</v>
+        <v>8.320700000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>2.956399999999999</v>
+        <v>2.9564</v>
       </c>
       <c r="M13" t="n">
         <v>-11.775</v>
@@ -1468,16 +1468,16 @@
         <v>14.1379</v>
       </c>
       <c r="S13" t="n">
-        <v>5.2155</v>
+        <v>5.215299999999999</v>
       </c>
       <c r="T13" t="n">
         <v>3.5812</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6342</v>
+        <v>1.6344</v>
       </c>
       <c r="V13" t="n">
-        <v>2.6504</v>
+        <v>2.650399999999999</v>
       </c>
       <c r="W13" t="n">
         <v>9.6462</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9424</v>
+        <v>1.6733</v>
       </c>
       <c r="E14" t="n">
-        <v>2.8967</v>
+        <v>3.2319</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.9543</v>
+        <v>-1.5587</v>
       </c>
       <c r="G14" t="n">
         <v>2.475</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.9422</v>
+        <v>-1.2113</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8099</v>
+        <v>-0.4747</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1322</v>
+        <v>-0.7367</v>
       </c>
       <c r="V14" t="n">
         <v>-0.678</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. MARTINEZ DIAZ</t>
+          <t>J. POWELL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5914</v>
+        <v>0.7047</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3481</v>
+        <v>-0.6496</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7567</v>
+        <v>1.3543</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.2359</v>
+        <v>2.8034</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1747</v>
+        <v>1.2073</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9388</v>
+        <v>1.5961</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9508</v>
+        <v>2.5932</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.3259</v>
+        <v>1.8067</v>
       </c>
       <c r="L15" t="n">
-        <v>2.2766</v>
+        <v>0.7865</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.1867</v>
+        <v>0.2102</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8488</v>
+        <v>-0.5994</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3379</v>
+        <v>0.8096</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0875</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3047</v>
+        <v>-0.2064</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0721</v>
+        <v>-0.1754</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2326</v>
+        <v>-0.031</v>
       </c>
       <c r="V15" t="n">
+        <v>-0.3698</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.1952</v>
+      </c>
+      <c r="X15" t="n">
         <v>-0.5649999999999999</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.3252</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-1.8902</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2908</v>
+        <v>0.4476</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9032</v>
+        <v>2.1267</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.6124</v>
+        <v>-1.6791</v>
       </c>
       <c r="G16" t="n">
         <v>0.5424</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6834</v>
+        <v>-0.5266</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.4494</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0105</v>
+        <v>-0.0772</v>
       </c>
       <c r="V16" t="n">
         <v>-0.8732</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. ALDERETE DIAZ</t>
+          <t>C. LUTETE IV</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0113</v>
+        <v>-0.0185</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0132</v>
+        <v>0.4801</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0245</v>
+        <v>-0.4985</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9771</v>
+        <v>0.9863</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.8767</v>
+        <v>0.0062</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1004</v>
+        <v>0.9802</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4278</v>
+        <v>2.6511</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5808</v>
+        <v>1.1195</v>
       </c>
       <c r="L17" t="n">
-        <v>0.153</v>
+        <v>1.5316</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5493</v>
+        <v>-1.6648</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.2959</v>
+        <v>-1.1134</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2534</v>
+        <v>-0.5514</v>
       </c>
       <c r="P17" t="n">
-        <v>1.9576</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.2626</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1438</v>
+        <v>-0.304</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4146</v>
+        <v>-0.0384</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2708</v>
+        <v>-0.2656</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.113</v>
+        <v>0.8218</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.113</v>
+        <v>-0.3082</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. POWELL</t>
+          <t>G. MARTINEZ DIAZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0068</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8731</v>
+        <v>2.1246</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8663</v>
+        <v>-2.1882</v>
       </c>
       <c r="G18" t="n">
-        <v>2.8034</v>
+        <v>-0.2359</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2073</v>
+        <v>-2.1747</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5961</v>
+        <v>1.9388</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5932</v>
+        <v>0.9508</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8067</v>
+        <v>-1.3259</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7865</v>
+        <v>2.2766</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2102</v>
+        <v>-1.1867</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5994</v>
+        <v>-0.8488</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8096</v>
+        <v>-0.3379</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.5225</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.918</v>
+        <v>-0.3503</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.399</v>
+        <v>-0.1514</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.519</v>
+        <v>-0.1989</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3698</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1952</v>
+        <v>1.3252</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.8902</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. LUTETE IV</t>
+          <t>D. ALDERETE DIAZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1187</v>
+        <v>-0.3047</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2565</v>
+        <v>-0.2367</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3753</v>
+        <v>-0.0679</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9863</v>
+        <v>-1.9771</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0062</v>
+        <v>-1.8767</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9802</v>
+        <v>-0.1004</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6511</v>
+        <v>-0.4278</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1195</v>
+        <v>-0.5808</v>
       </c>
       <c r="L19" t="n">
-        <v>1.5316</v>
+        <v>0.153</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6648</v>
+        <v>-1.5493</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1134</v>
+        <v>-1.2959</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5514</v>
+        <v>-0.2534</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5225</v>
+        <v>1.9576</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.2626</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4043</v>
+        <v>-0.1721</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.262</v>
+        <v>0.1911</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1423</v>
+        <v>-0.3632</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8218</v>
+        <v>-0.113</v>
       </c>
       <c r="W19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3082</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8243</v>
+        <v>-0.4159</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0399</v>
+        <v>0.2635</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8643</v>
+        <v>-0.6793</v>
       </c>
       <c r="G20" t="n">
         <v>0.5216</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3682</v>
+        <v>0.0403</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1935</v>
+        <v>0.03</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1747</v>
+        <v>0.0102</v>
       </c>
       <c r="V20" t="n">
         <v>-0.7602</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8649</v>
+        <v>-1.1243</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9517</v>
+        <v>-1.1752</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0868</v>
+        <v>0.0508</v>
       </c>
       <c r="G21" t="n">
         <v>-1.5735</v>
@@ -2092,13 +2092,13 @@
         <v>2.3926</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5259</v>
+        <v>-0.7853</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1334</v>
+        <v>-0.3569</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3925</v>
+        <v>-0.4284</v>
       </c>
       <c r="V21" t="n">
         <v>1.017</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. LUGARINI</t>
+          <t>P. HERNANDEZ MONTENEGRO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1419</v>
+        <v>-2.3298</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1962</v>
+        <v>-1.188</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9456</v>
+        <v>-1.1418</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.6592</v>
+        <v>-1.3852</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1867</v>
+        <v>-0.1127</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5275</v>
+        <v>-1.2726</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3075</v>
+        <v>-0.7125</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9395</v>
+        <v>0.2222</v>
       </c>
       <c r="L22" t="n">
-        <v>0.6319</v>
+        <v>-0.9347</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.3517</v>
+        <v>-0.6727</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.2473</v>
+        <v>-0.3348</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1044</v>
+        <v>-0.3379</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8649</v>
+        <v>-0.9445</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0911</v>
+        <v>-0.5179</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2263</v>
+        <v>-0.4266</v>
       </c>
       <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X22" t="n">
         <v>-1.13</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.1952</v>
-      </c>
-      <c r="X22" t="n">
-        <v>-1.3252</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. HERNANDEZ MONTENEGRO</t>
+          <t>B. LUGARINI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0722</v>
+        <v>-3.0166</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4115</v>
+        <v>-1.9785</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6606</v>
+        <v>-1.0381</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3852</v>
+        <v>-1.6592</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1127</v>
+        <v>-2.1867</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.2726</v>
+        <v>0.5275</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7125</v>
+        <v>-0.3075</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2222</v>
+        <v>-0.9395</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9347</v>
+        <v>0.6319</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6727</v>
+        <v>-1.3517</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3348</v>
+        <v>-1.2473</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3379</v>
+        <v>-0.1044</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0875</v>
+        <v>1.9576</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6869</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>0.3088</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9455</v>
+        <v>-0.3188</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.13</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="24">
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.1929</v>
+        <v>-4.4479</v>
       </c>
       <c r="E24" t="n">
-        <v>2.998699999999999</v>
+        <v>2.998800000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.191599999999999</v>
+        <v>-7.446499999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4978000000000002</v>
+        <v>0.4977999999999991</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1599</v>
+        <v>-2.159899999999999</v>
       </c>
       <c r="I24" t="n">
         <v>2.6576</v>
@@ -2311,7 +2311,7 @@
         <v>-11.2774</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.3209</v>
+        <v>-8.320900000000002</v>
       </c>
       <c r="O24" t="n">
         <v>-2.9565</v>
@@ -2326,16 +2326,16 @@
         <v>16.3131</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.2155</v>
+        <v>-4.4701</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.6343</v>
+        <v>-1.6342</v>
       </c>
       <c r="U24" t="n">
-        <v>-3.5812</v>
+        <v>-2.8362</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.650399999999999</v>
+        <v>-2.6504</v>
       </c>
       <c r="W24" t="n">
         <v>6.9958</v>
